--- a/artfynd/A 69362-2020 artfynd.xlsx
+++ b/artfynd/A 69362-2020 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 69362-2020 artfynd.xlsx
+++ b/artfynd/A 69362-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121671533</v>
       </c>
       <c r="B2" t="n">
-        <v>57273</v>
+        <v>57281</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 69362-2020 artfynd.xlsx
+++ b/artfynd/A 69362-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121671533</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
+        <v>57285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 69362-2020 artfynd.xlsx
+++ b/artfynd/A 69362-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121671533</v>
       </c>
       <c r="B2" t="n">
-        <v>57285</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 69362-2020 artfynd.xlsx
+++ b/artfynd/A 69362-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121671533</v>
       </c>
       <c r="B2" t="n">
-        <v>57288</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 69362-2020 artfynd.xlsx
+++ b/artfynd/A 69362-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121671533</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>57295</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
